--- a/HUS_APP/Historias_de_Usuario.xlsx
+++ b/HUS_APP/Historias_de_Usuario.xlsx
@@ -65,7 +65,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -87,11 +87,55 @@
         <color rgb="00B4B4B4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +161,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D21"/>
+  <dimension ref="B2:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -748,6 +794,23 @@
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>HU0019 - Confirmar cada cambio</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>EPICA0010</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Recuperacion de acceso y administracion de cuentas</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>HU0020 - Solicitar el restablecimiento de contrasena</t>
         </is>
       </c>
     </row>
@@ -762,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -786,11 +849,22 @@
           <t>Enunciado de la Historia</t>
         </is>
       </c>
+      <c r="B1" s="9" t="n"/>
+      <c r="C1" s="9" t="n"/>
+      <c r="D1" s="9" t="n"/>
+      <c r="E1" s="9" t="n"/>
+      <c r="F1" s="9" t="n"/>
+      <c r="G1" s="9" t="n"/>
+      <c r="H1" s="9" t="n"/>
+      <c r="I1" s="10" t="n"/>
       <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Criterios de Aceptación</t>
         </is>
       </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="10" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1650,22 +1724,22 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Edición exitosa</t>
+          <t>Edicion exitosa y verificable</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>El usuario abre el modal de edición de un estudiante</t>
+          <t>El usuario abre la edicion de un estudiante ya registrado</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Modifica uno o más campos y confirma en el diálogo</t>
+          <t>Modifica uno o varios de los campos editables (nombre, apellido, edad, nivel, grado, ano de cursada, genero, contacto de emergencia, tipo y numero de documento) y confirma en el dialogo</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>El sistema guarda los cambios y muestra «Alumno actualizado correctamente»</t>
+          <t>El sistema guarda los cambios, muestra «Alumno actualizado correctamente» y el listado refleja de inmediato los valores nuevos, de modo que el resultado se puede verificar sin recargar la pagina</t>
         </is>
       </c>
     </row>
@@ -1750,105 +1824,70 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>HU0007</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Docente o Administrador</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>eliminar un estudiante que se registró por error</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>mantener limpio el padrón sin perder información válida</t>
-        </is>
-      </c>
-      <c r="G22" s="5">
-        <f>CONCATENATE("Como ",B22," quiero ",D22," para ",F22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="7">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HU0006</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22">
         <f>CONCATENATE(A22,"-",H22)</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Eliminación de un registro sin historial</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>El estudiante no tiene notas, encuestas, predicciones ni expediente</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>El usuario pulsa «Eliminar» y confirma</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>El sistema elimina el registro y actualiza el listado</t>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Validacion al editar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>El usuario esta editando un estudiante</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Escribe una edad fuera del rango 11-12, o un grado que no corresponde al nivel elegido</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>El sistema rechaza el guardado —422 cuando el valor incumple el formato del campo, como una edad fuera de 11-12; 400 cuando la combinacion no es valida, como un grado que no corresponde al nivel— explicando el motivo, y los datos anteriores del estudiante permanecen sin cambios</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>HU0007</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="7">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HU0006</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23">
         <f>CONCATENATE(A23,"-",H23)</f>
         <v/>
       </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Eliminación bloqueada por historial</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>El estudiante tiene notas, encuestas o predicciones registradas</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>El usuario pulsa «Eliminar» y confirma</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>El sistema responde 409 detallando cuántos registros de cada tipo lo impiden</t>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Cancelacion de la edicion</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>El usuario ha modificado campos pero aun no ha confirmado</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Pulsa «Cancelar» o cierra el dialogo con Escape</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No se envia ninguna peticion y el estudiante conserva sus valores originales</t>
         </is>
       </c>
     </row>
@@ -1858,14 +1897,37 @@
           <t>HU0007</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Docente o Administrador</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>eliminar un estudiante que se registró por error</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>mantener limpio el padrón sin perder información válida</t>
+        </is>
+      </c>
+      <c r="G24" s="5">
+        <f>CONCATENATE("Como ",B24," quiero ",D24," para ",F24)</f>
+        <v/>
+      </c>
       <c r="H24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" s="7">
         <f>CONCATENATE(A24,"-",H24)</f>
@@ -1873,62 +1935,39 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Aviso previo en la interfaz</t>
+          <t>Eliminacion de un registro sin historial</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>El estudiante tiene historial asociado</t>
+          <t>El estudiante seleccionado no tiene notas, encuestas, predicciones ni expediente</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>El usuario pulsa «Eliminar»</t>
+          <t>El usuario pulsa «Eliminar» y confirma en el dialogo</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>El diálogo advierte de que no se podrá eliminar antes de que el usuario confirme</t>
+          <t>El sistema responde 204, retira al estudiante del listado y el total de registrados disminuye en uno</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>HU0008</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Psicólogo</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>registrar los 20 ítems de la escala EDAH de un estudiante</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>obtener la estimación de probabilidad de TDAH</t>
-        </is>
-      </c>
-      <c r="G25" s="5">
-        <f>CONCATENATE("Como ",B25," quiero ",D25," para ",F25)</f>
-        <v/>
-      </c>
+          <t>HU0007</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="7">
         <f>CONCATENATE(A25,"-",H25)</f>
@@ -1936,29 +1975,29 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>Encuesta completa</t>
+          <t>Eliminacion bloqueada, sin borrado en cascada</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>El psicólogo selecciona un estudiante y responde los 20 ítems</t>
+          <t>El estudiante tiene notas, encuestas o predicciones registradas</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Confirma el guardado en el diálogo</t>
+          <t>El usuario pulsa «Eliminar» y confirma</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>El sistema guarda la encuesta y habilita la generación de la predicción</t>
+          <t>El sistema responde 409 SIN borrar nada: ni el estudiante ni sus notas, encuestas, predicciones, inasistencias o expediente. El mensaje enumera cuantos registros de cada tipo lo impiden. Para darlo de baja hay que retirar antes ese historial de forma deliberada</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>HU0008</t>
+          <t>HU0007</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr"/>
@@ -1968,7 +2007,7 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="7">
         <f>CONCATENATE(A26,"-",H26)</f>
@@ -1976,62 +2015,56 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Ítem fuera de escala</t>
+          <t>Aviso previo en la interfaz</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Se envía un ítem con valor 4</t>
+          <t>El estudiante tiene historial asociado</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Se intenta guardar la encuesta</t>
+          <t>El usuario pulsa «Eliminar»</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>El sistema rechaza el envío: los ítems solo admiten valores de 0 a 3</t>
+          <t>El diálogo advierte de que no se podrá eliminar antes de que el usuario confirme</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>HU0008</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="7">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HU0007</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27">
         <f>CONCATENATE(A27,"-",H27)</f>
         <v/>
       </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>Ítem sin responder</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Falta uno de los 20 ítems</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Se intenta guardar la encuesta</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>El sistema indica que el campo es obligatorio y no guarda</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Cancelacion de la eliminacion</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>El dialogo de confirmacion de borrado esta abierto</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>El usuario pulsa «Cancelar» o la tecla Escape</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No se envia ninguna peticion, el estudiante sigue registrado y el listado no cambia. El foco inicial del dialogo esta en «Cancelar» para que un Enter accidental no ejecute el borrado</t>
         </is>
       </c>
     </row>
@@ -2041,14 +2074,37 @@
           <t>HU0008</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Psicólogo</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>registrar los 20 ítems de la escala EDAH de un estudiante</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>obtener la estimación de probabilidad de TDAH</t>
+        </is>
+      </c>
+      <c r="G28" s="5">
+        <f>CONCATENATE("Como ",B28," quiero ",D28," para ",F28)</f>
+        <v/>
+      </c>
       <c r="H28" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" s="7">
         <f>CONCATENATE(A28,"-",H28)</f>
@@ -2056,62 +2112,39 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>Estudiante inexistente</t>
+          <t>Encuesta completa</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Se envía la encuesta con un identificador de estudiante que no existe</t>
+          <t>El psicólogo selecciona un estudiante y responde los 20 ítems</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Se intenta guardar</t>
+          <t>Confirma el guardado en el diálogo</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>El sistema responde 404 «Alumno no encontrado»</t>
+          <t>El sistema guarda la encuesta y habilita la generación de la predicción</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HU0009</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Docente</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>registrar los días de inasistencia acumulados de un estudiante</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>que el modelo de riesgo académico los tenga en cuenta</t>
-        </is>
-      </c>
-      <c r="G29" s="5">
-        <f>CONCATENATE("Como ",B29," quiero ",D29," para ",F29)</f>
-        <v/>
-      </c>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="7">
         <f>CONCATENATE(A29,"-",H29)</f>
@@ -2119,29 +2152,29 @@
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>Registro exitoso</t>
+          <t>Item fuera de la escala EDAH</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>El docente selecciona un estudiante y escribe los días</t>
+          <t>Se envia un item con un valor distinto de 0, 1, 2 o 3</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Confirma en el diálogo</t>
+          <t>Se intenta guardar la encuesta</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>El sistema guarda el valor y recalcula la predicción del estudiante</t>
+          <t>El sistema rechaza el envio con 422 indicando que los items solo admiten valores de 0 a 3. Los totales por subescala (DA, HI, TC) los calcula el sistema al guardar; no son campos que el usuario introduzca ni pueda corregir</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>HU0009</t>
+          <t>HU0008</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
@@ -2151,7 +2184,7 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="7">
         <f>CONCATENATE(A30,"-",H30)</f>
@@ -2159,29 +2192,29 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>Valor negativo</t>
+          <t>No se admite una encuesta incompleta</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>El docente escribe un número negativo</t>
+          <t>Falta por responder al menos uno de los 20 items</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Intenta guardar</t>
+          <t>Se intenta guardar la encuesta</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>El sistema rechaza el valor: debe ser un entero mayor o igual a 0</t>
+          <t>El sistema rechaza el guardado con 422 y no almacena nada parcial: el EDAH solo es interpretable completo, y una encuesta a medias produciria una puntuacion falsamente baja. No existe la figura de borrador</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>HU0009</t>
+          <t>HU0008</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
@@ -2191,7 +2224,7 @@
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
         <f>CONCATENATE(A31,"-",H31)</f>
@@ -2199,182 +2232,164 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>Valor por encima del año lectivo</t>
+          <t>Estudiante inexistente</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>El docente escribe 366 días</t>
+          <t>Se envía la encuesta con un identificador de estudiante que no existe</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Intenta guardar</t>
+          <t>Se intenta guardar</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>El sistema rechaza el valor por superar el máximo de 365</t>
+          <t>El sistema responde 404 «Alumno no encontrado»</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>HU0009</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" s="7">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32">
         <f>CONCATENATE(A32,"-",H32)</f>
         <v/>
       </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>Estudiante sin encuesta EDAH</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>El estudiante no tiene encuesta registrada</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>El docente guarda sus inasistencias</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>El sistema guarda el valor e informa de que la predicción se generará cuando exista la encuesta</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Se registra quien responde la escala</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>El EDAH lo responde un adulto que observa al estudiante a diario, no el propio estudiante</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Se guarda la encuesta indicando el informante: docente, familiar o psicologo por observacion directa</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>El sistema almacena el informante junto a la encuesta y lo muestra al consultarla. Una misma puntuacion no se interpreta igual segun quien la responda, porque la conducta en clase y en casa no son lo mismo</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>HU0010</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Docente</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>registrar las calificaciones literales de cada área curricular</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>que el promedio alimente la predicción de riesgo académico</t>
-        </is>
-      </c>
-      <c r="G33" s="5">
-        <f>CONCATENATE("Como ",B33," quiero ",D33," para ",F33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="7">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33">
         <f>CONCATENATE(A33,"-",H33)</f>
         <v/>
       </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>Registro exitoso</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>El docente selecciona estudiante y bimestre y completa las notas</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>Confirma en el diálogo</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>El sistema guarda las notas, calcula el promedio y recalcula el riesgo</t>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Informante no admitido</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Se envia un informante que no esta en la lista prevista</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Se intenta guardar la encuesta</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>El sistema rechaza el envio con 422 y enumera los informantes admitidos</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>HU0010</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="7">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>7</v>
+      </c>
+      <c r="I34">
         <f>CONCATENATE(A34,"-",H34)</f>
         <v/>
       </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>Calificación no válida</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>El docente introduce una calificación distinta de AD, A, B o C</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>Intenta guardar</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>El sistema rechaza la calificación indicando los valores admitidos</t>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Reaplicacion: se usa siempre la mas reciente</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>El estudiante ya tiene una encuesta registrada</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Se registra una encuesta nueva para el mismo estudiante</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>El sistema NO sobrescribe la anterior: la conserva y anade la nueva, porque el EDAH se reaplica en el tiempo y comparar dos momentos es parte de la evaluacion. Las predicciones usan siempre la mas reciente por fecha, y a igualdad de fecha la ultima registrada. Una encuesta guardada no se puede corregir: si hubo un error, se aplica de nuevo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>HU0010</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
+          <t>HU0009</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>registrar los días de inasistencia acumulados de un estudiante</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>que el modelo de riesgo académico los tenga en cuenta</t>
+        </is>
+      </c>
+      <c r="G35" s="5">
+        <f>CONCATENATE("Como ",B35," quiero ",D35," para ",F35)</f>
+        <v/>
+      </c>
       <c r="H35" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" s="7">
         <f>CONCATENATE(A35,"-",H35)</f>
@@ -2382,29 +2397,29 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>Área ajena al plan de estudios</t>
+          <t>Registro de los dias del ano lectivo</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Se envía un área curricular que no pertenece al Currículo Nacional</t>
+          <t>El docente selecciona un estudiante y consulta su valor vigente</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Se intenta guardar la nota</t>
+          <t>Escribe los dias de inasistencia acumulados en el ano lectivo y confirma</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>El sistema rechaza el registro y enumera las áreas válidas</t>
+          <t>El sistema guarda el valor, deja constancia del cambio en el historial y recalcula la prediccion. La interfaz indica que el periodo es el ano lectivo completo, no el bimestre, y que el maximo admitido es 365 dias</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>HU0010</t>
+          <t>HU0009</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr"/>
@@ -2414,7 +2429,7 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" s="7">
         <f>CONCATENATE(A36,"-",H36)</f>
@@ -2422,62 +2437,39 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>Bimestre fuera de rango</t>
+          <t>Valor negativo</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Se envía el bimestre 5</t>
+          <t>El docente escribe un número negativo</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Se intenta guardar la nota</t>
+          <t>Intenta guardar</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>El sistema rechaza el valor: solo admite 1, 2, 3 o 4</t>
+          <t>El sistema rechaza el valor: debe ser un entero mayor o igual a 0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>HU0011</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Docente</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>cargar las notas de todo un grado desde un archivo CSV o Excel</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>ahorrar el registro manual de cientos de calificaciones</t>
-        </is>
-      </c>
-      <c r="G37" s="5">
-        <f>CONCATENATE("Como ",B37," quiero ",D37," para ",F37)</f>
-        <v/>
-      </c>
+          <t>HU0009</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="7">
         <f>CONCATENATE(A37,"-",H37)</f>
@@ -2485,29 +2477,29 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>Archivo procesado</t>
+          <t>Valor por encima del año lectivo</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>El docente selecciona un archivo con el formato de la plantilla</t>
+          <t>El docente escribe 366 días</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Confirma el procesamiento en el diálogo</t>
+          <t>Intenta guardar</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>El sistema guarda las filas válidas e informa de cuántas se procesaron</t>
+          <t>El sistema rechaza el valor por superar el máximo de 365</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>HU0011</t>
+          <t>HU0009</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr"/>
@@ -2517,7 +2509,7 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
         <f>CONCATENATE(A38,"-",H38)</f>
@@ -2525,142 +2517,130 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>Validación fila por fila</t>
+          <t>Estudiante sin encuesta EDAH</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>El archivo contiene filas correctas y filas con errores</t>
+          <t>El estudiante no tiene encuesta registrada</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>El docente procesa el archivo</t>
+          <t>El docente guarda sus inasistencias</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>El sistema guarda las correctas y detalla el motivo del rechazo de cada fila inválida</t>
+          <t>El sistema guarda el valor e informa de que la predicción se generará cuando exista la encuesta</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>HU0011</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="7">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HU0009</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39">
         <f>CONCATENATE(A39,"-",H39)</f>
         <v/>
       </c>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>Descarga de la plantilla</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>El docente no conoce el formato esperado</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>Pulsa «Descargar plantilla»</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>El sistema entrega un CSV con las columnas alumno_id, bimestre, asignatura y calificación</t>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Consulta del historial de cambios</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>El docente selecciona un estudiante en Control de Inasistencias</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Consulta el panel de historial</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>El sistema muestra cada cambio del contador con su valor anterior, el nuevo, la diferencia, la fecha y quien lo registro. Sin esto solo se conservaria el ultimo numero y no habria forma de distinguir una correccion de captura de un empeoramiento real del estudiante</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>HU0012</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Usuario del sistema</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>generar la predicción de TDAH y de riesgo académico de un estudiante</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>identificar a tiempo a quien necesita acompañamiento</t>
-        </is>
-      </c>
-      <c r="G40" s="5">
-        <f>CONCATENATE("Como ",B40," quiero ",D40," para ",F40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="7">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HU0009</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40">
         <f>CONCATENATE(A40,"-",H40)</f>
         <v/>
       </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>Predicción generada</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>El estudiante tiene encuesta EDAH registrada</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>El usuario pulsa «Generar predicción» y confirma</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>El sistema ejecuta ambos modelos y guarda el resultado en el historial</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Aviso ante un salto grande</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Se registra un cambio de 15 dias o mas en una sola anotacion</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>El docente consulta el historial</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>El sistema destaca ese movimiento, porque un salto asi se parece tanto a un mes de ausencias real como a un cero de mas al teclear, y la cifra alimenta el modelo de riesgo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HU0012</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
+          <t>HU0010</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>registrar las calificaciones literales de cada área curricular</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>que el promedio alimente la predicción de riesgo académico</t>
+        </is>
+      </c>
+      <c r="G41" s="5">
+        <f>CONCATENATE("Como ",B41," quiero ",D41," para ",F41)</f>
+        <v/>
+      </c>
       <c r="H41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="7">
         <f>CONCATENATE(A41,"-",H41)</f>
@@ -2668,29 +2648,29 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>Estudiante sin encuesta</t>
+          <t>Registro exitoso</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>El estudiante no tiene encuesta EDAH</t>
+          <t>El docente selecciona estudiante y bimestre y completa las notas</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>El usuario intenta generar la predicción</t>
+          <t>Confirma en el diálogo</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>El sistema informa de que primero debe registrarse la encuesta</t>
+          <t>El sistema guarda las notas, calcula el promedio y recalcula el riesgo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>HU0012</t>
+          <t>HU0010</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr"/>
@@ -2700,7 +2680,7 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" s="7">
         <f>CONCATENATE(A42,"-",H42)</f>
@@ -2708,62 +2688,39 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>Estudiante inexistente</t>
+          <t>Calificación no válida</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Se solicita la predicción de un identificador que no existe</t>
+          <t>El docente introduce una calificación distinta de AD, A, B o C</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>Se envía la petición</t>
+          <t>Intenta guardar</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>El sistema responde 404 «Alumno no encontrado»</t>
+          <t>El sistema rechaza la calificación indicando los valores admitidos</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>HU0013</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Usuario del sistema</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>consultar todas las predicciones registradas de un estudiante</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>observar su evolución a lo largo del tiempo</t>
-        </is>
-      </c>
-      <c r="G43" s="5">
-        <f>CONCATENATE("Como ",B43," quiero ",D43," para ",F43)</f>
-        <v/>
-      </c>
+          <t>HU0010</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" s="7">
         <f>CONCATENATE(A43,"-",H43)</f>
@@ -2771,29 +2728,29 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>Historial con filtros</t>
+          <t>Área ajena al plan de estudios</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>El estudiante tiene varias predicciones registradas</t>
+          <t>Se envía un área curricular que no pertenece al Currículo Nacional</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>El usuario abre «Historial de Predicciones» y aplica filtros</t>
+          <t>Se intenta guardar la nota</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>El sistema muestra las predicciones que cumplen los filtros, de la más reciente a la más antigua</t>
+          <t>El sistema rechaza el registro y enumera las áreas válidas</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>HU0013</t>
+          <t>HU0010</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr"/>
@@ -2803,7 +2760,7 @@
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
         <f>CONCATENATE(A44,"-",H44)</f>
@@ -2811,34 +2768,34 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>Estudiante sin predicciones</t>
+          <t>Bimestre fuera de rango</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>El estudiante no tiene ninguna predicción</t>
+          <t>Se envía el bimestre 5</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>El usuario consulta su historial</t>
+          <t>Se intenta guardar la nota</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>El sistema indica que no hay predicciones registradas</t>
+          <t>El sistema rechaza el valor: solo admite 1, 2, 3 o 4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HU0014</t>
+          <t>HU0011</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Psicólogo o Docente</t>
+          <t>Docente</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2848,7 +2805,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>conocer qué factores pesaron en la predicción</t>
+          <t>cargar las notas de todo un grado desde un archivo CSV o Excel</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2858,7 +2815,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>poder justificar la decisión ante la familia y el colegio</t>
+          <t>ahorrar el registro manual de cientos de calificaciones</t>
         </is>
       </c>
       <c r="G45" s="5">
@@ -2874,29 +2831,29 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>Explicación por subescalas</t>
+          <t>Archivo procesado</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Existe una predicción de TDAH registrada</t>
+          <t>El docente selecciona un archivo con el formato de la plantilla</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>El usuario consulta su explicación</t>
+          <t>Confirma el procesamiento en el diálogo</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>El sistema muestra el aporte de las subescalas de atención, hiperactividad y trastorno de conducta</t>
+          <t>El sistema guarda las filas válidas e informa de cuántas se procesaron</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>HU0014</t>
+          <t>HU0011</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr"/>
@@ -2914,29 +2871,29 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Explicación del riesgo académico</t>
+          <t>Validación fila por fila</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Existe una predicción de riesgo registrada</t>
+          <t>El archivo contiene filas correctas y filas con errores</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>El usuario consulta su explicación</t>
+          <t>El docente procesa el archivo</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>El sistema muestra el aporte del promedio, las inasistencias y la probabilidad de TDAH</t>
+          <t>El sistema guarda las correctas y detalla el motivo del rechazo de cada fila inválida</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>HU0014</t>
+          <t>HU0011</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr"/>
@@ -2954,29 +2911,29 @@
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>Recomendaciones prescriptivas</t>
+          <t>Descarga de la plantilla</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Existe una predicción registrada</t>
+          <t>El docente no conoce el formato esperado</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>El usuario consulta las recomendaciones</t>
+          <t>Pulsa «Descargar plantilla»</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>El sistema propone acciones concretas según el nivel de riesgo y la probabilidad de TDAH</t>
+          <t>El sistema entrega un CSV con las columnas alumno_id, bimestre, asignatura y calificación</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>HU0015</t>
+          <t>HU0012</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2991,7 +2948,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>ver el estado general de todos los estudiantes evaluados</t>
+          <t>generar la predicción de TDAH y de riesgo académico de un estudiante</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3001,7 +2958,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>priorizar la atención con una visión de conjunto</t>
+          <t>identificar a tiempo a quien necesita acompañamiento</t>
         </is>
       </c>
       <c r="G48" s="5">
@@ -3017,29 +2974,29 @@
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>Panorama general</t>
+          <t>Predicción generada</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Existen estudiantes con predicciones registradas</t>
+          <t>El estudiante tiene encuesta EDAH registrada</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>El usuario abre «Dashboard General»</t>
+          <t>El usuario pulsa «Generar predicción» y confirma</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>El sistema muestra los indicadores agregados y la distribución por nivel de riesgo y de TDAH</t>
+          <t>El sistema ejecuta ambos modelos y guarda el resultado en el historial</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>HU0015</t>
+          <t>HU0012</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr"/>
@@ -3057,62 +3014,39 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>Filtros combinados</t>
+          <t>Estudiante sin encuesta</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>El usuario quiere ver solo un subconjunto</t>
+          <t>El estudiante no tiene encuesta EDAH</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>Aplica los filtros de grado, riesgo y probabilidad de TDAH</t>
+          <t>El usuario intenta generar la predicción</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>El sistema muestra únicamente los estudiantes que cumplen todos los filtros a la vez</t>
+          <t>El sistema informa de que primero debe registrarse la encuesta</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>HU0016</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Usuario del sistema</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>buscar un estudiante y ver su panel individual</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>revisar su situación concreta sin recorrer toda la lista</t>
-        </is>
-      </c>
-      <c r="G50" s="5">
-        <f>CONCATENATE("Como ",B50," quiero ",D50," para ",F50)</f>
-        <v/>
-      </c>
+          <t>HU0012</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" s="7">
         <f>CONCATENATE(A50,"-",H50)</f>
@@ -3120,79 +3054,96 @@
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Búsqueda por nombre</t>
+          <t>Estudiante inexistente</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Existen estudiantes registrados</t>
+          <t>Se solicita la predicción de un identificador que no existe</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>El usuario escribe un nombre y pulsa «Buscar»</t>
+          <t>Se envía la petición</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>El sistema acota la lista a los estudiantes cuyo nombre o apellido contiene el texto</t>
+          <t>El sistema responde 404 «Alumno no encontrado»</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>HU0016</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" s="7">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HU0012</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>4</v>
+      </c>
+      <c r="I51">
         <f>CONCATENATE(A51,"-",H51)</f>
         <v/>
       </c>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>Cambios sin aplicar</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>El usuario modifica un filtro y todavía no pulsa «Buscar»</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>Observa la pantalla</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>El sistema advierte «Cambios sin aplicar» para que sepa que el resultado aún no se ha actualizado</t>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Cualquier rol con acceso puede generarla</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Tanto el docente como el psicologo y el administrador tienen la vista de predicciones</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Cualquiera de ellos solicita generar la prediccion de un estudiante</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>El sistema la genera sin distinguir el rol: no es un acto clinico reservado, sino el calculo de un modelo. Ademas se regenera sola cuando cambian las notas o las inasistencias, de modo que tambien la desencadena el docente sin pedirla expresamente</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>HU0016</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr"/>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
+          <t>HU0013</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Usuario del sistema</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>consultar todas las predicciones registradas de un estudiante</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>observar su evolución a lo largo del tiempo</t>
+        </is>
+      </c>
+      <c r="G52" s="5">
+        <f>CONCATENATE("Como ",B52," quiero ",D52," para ",F52)</f>
+        <v/>
+      </c>
       <c r="H52" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52" s="7">
         <f>CONCATENATE(A52,"-",H52)</f>
@@ -3200,29 +3151,29 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Sin coincidencias</t>
+          <t>Historial con filtros</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Ningún estudiante cumple los filtros</t>
+          <t>El estudiante tiene varias predicciones registradas</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>El usuario pulsa «Buscar»</t>
+          <t>El usuario abre «Historial de Predicciones» y aplica filtros</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>El sistema informa de que ningún estudiante cumple los filtros y sugiere revisarlos</t>
+          <t>El sistema muestra las predicciones que cumplen los filtros, de la más reciente a la más antigua</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>HU0016</t>
+          <t>HU0013</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
@@ -3232,7 +3183,7 @@
       <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53" s="7">
         <f>CONCATENATE(A53,"-",H53)</f>
@@ -3240,34 +3191,34 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>Limpiar filtros</t>
+          <t>Estudiante sin predicciones</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Hay filtros aplicados</t>
+          <t>El estudiante no tiene ninguna predicción</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>El usuario pulsa «Limpiar filtros»</t>
+          <t>El usuario consulta su historial</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>El sistema restablece todos los filtros y vuelve a mostrar la lista completa</t>
+          <t>El sistema indica que no hay predicciones registradas</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>HU0017</t>
+          <t>HU0014</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Psicólogo</t>
+          <t>Psicólogo o Docente</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -3277,7 +3228,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>descargar el expediente completo de un estudiante</t>
+          <t>conocer qué factores pesaron en la predicción</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3287,7 +3238,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>archivarlo y compartirlo con la familia</t>
+          <t>poder justificar la decisión ante la familia y el colegio</t>
         </is>
       </c>
       <c r="G54" s="5">
@@ -3303,29 +3254,29 @@
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Descarga exitosa</t>
+          <t>Explicación por subescalas</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>El estudiante tiene encuesta y predicción registradas</t>
+          <t>Existe una predicción de TDAH registrada</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>El psicólogo pulsa «Descargar Expediente»</t>
+          <t>El usuario consulta su explicación</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>El sistema genera el documento con los datos, los resultados y su explicación</t>
+          <t>El sistema muestra el aporte de las subescalas de atención, hiperactividad y trastorno de conducta</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>HU0017</t>
+          <t>HU0014</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr"/>
@@ -3343,62 +3294,39 @@
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>Estudiante sin datos suficientes</t>
+          <t>Explicación del riesgo académico</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>El estudiante no tiene predicción registrada</t>
+          <t>Existe una predicción de riesgo registrada</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>El psicólogo intenta descargar el expediente</t>
+          <t>El usuario consulta su explicación</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>El sistema informa de qué información falta antes de poder generarlo</t>
+          <t>El sistema muestra el aporte del promedio, las inasistencias y la probabilidad de TDAH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>HU0018</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Administrador</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Necesito:</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>que el documento de identidad se guarde cifrado</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Con la finalidad de:</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>cumplir la Ley N.° 29733 de protección de datos personales</t>
-        </is>
-      </c>
-      <c r="G56" s="5">
-        <f>CONCATENATE("Como ",B56," quiero ",D56," para ",F56)</f>
-        <v/>
-      </c>
+          <t>HU0014</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr"/>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" s="7">
         <f>CONCATENATE(A56,"-",H56)</f>
@@ -3406,39 +3334,62 @@
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Cifrado en la base de datos</t>
+          <t>Recomendaciones prescriptivas</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Se registra un estudiante con su documento</t>
+          <t>Existe una predicción registrada</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>Se consulta directamente la base de datos</t>
+          <t>El usuario consulta las recomendaciones</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>El número no es legible: se almacena cifrado con Fernet</t>
+          <t>El sistema propone acciones concretas según el nivel de riesgo y la probabilidad de TDAH</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>HU0018</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr"/>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
+          <t>HU0015</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Usuario del sistema</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>ver el estado general de todos los estudiantes evaluados</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>priorizar la atención con una visión de conjunto</t>
+        </is>
+      </c>
+      <c r="G57" s="5">
+        <f>CONCATENATE("Como ",B57," quiero ",D57," para ",F57)</f>
+        <v/>
+      </c>
       <c r="H57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="7">
         <f>CONCATENATE(A57,"-",H57)</f>
@@ -3446,29 +3397,29 @@
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Unicidad sin exponer el dato</t>
+          <t>Panorama general</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>Se intenta registrar un documento ya existente</t>
+          <t>Existen estudiantes con predicciones registradas</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Se envía el formulario</t>
+          <t>El usuario abre «Dashboard General»</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>El sistema detecta el duplicado mediante una huella irreversible, sin descifrar ningún dato</t>
+          <t>El sistema muestra los indicadores agregados y la distribución por nivel de riesgo y de TDAH</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>HU0018</t>
+          <t>HU0015</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr"/>
@@ -3478,7 +3429,7 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" s="7">
         <f>CONCATENATE(A58,"-",H58)</f>
@@ -3486,29 +3437,29 @@
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>Enmascarado en la interfaz y en la API</t>
+          <t>Filtros combinados</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Se consulta el listado de estudiantes</t>
+          <t>El usuario quiere ver solo un subconjunto</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Se observa la respuesta de la API</t>
+          <t>Aplica los filtros de grado, riesgo y probabilidad de TDAH</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>El número completo no viaja en el listado: solo los cuatro últimos caracteres</t>
+          <t>El sistema muestra únicamente los estudiantes que cumplen todos los filtros a la vez</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>HU0019</t>
+          <t>HU0016</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3523,7 +3474,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>que el sistema me pida confirmación antes de modificar datos</t>
+          <t>buscar un estudiante y ver su panel individual</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3533,7 +3484,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>evitar cambios accidentales sobre información de menores</t>
+          <t>revisar su situación concreta sin recorrer toda la lista</t>
         </is>
       </c>
       <c r="G59" s="5">
@@ -3549,29 +3500,29 @@
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>Confirmación antes de guardar</t>
+          <t>Búsqueda por nombre</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>El usuario completa cualquier formulario que modifica datos</t>
+          <t>Existen estudiantes registrados</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>Pulsa el botón de guardar</t>
+          <t>El usuario escribe un nombre y pulsa «Buscar»</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>El sistema muestra un diálogo con el detalle de lo que va a ocurrir antes de ejecutarlo</t>
+          <t>El sistema acota la lista a los estudiantes cuyo nombre o apellido contiene el texto</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>HU0019</t>
+          <t>HU0016</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
@@ -3589,29 +3540,29 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>Cancelación sin efectos</t>
+          <t>Cambios sin aplicar</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>El diálogo de confirmación está abierto</t>
+          <t>El usuario modifica un filtro y todavía no pulsa «Buscar»</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>El usuario pulsa «Cancelar» o la tecla Escape</t>
+          <t>Observa la pantalla</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>No se envía ninguna petición y los datos permanecen sin cambios</t>
+          <t>El sistema advierte «Cambios sin aplicar» para que sepa que el resultado aún no se ha actualizado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>HU0019</t>
+          <t>HU0016</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr"/>
@@ -3629,22 +3580,1263 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
+          <t>Sin coincidencias</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Ningún estudiante cumple los filtros</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>El usuario pulsa «Buscar»</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>El sistema informa de que ningún estudiante cumple los filtros y sugiere revisarlos</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>HU0016</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" s="7">
+        <f>CONCATENATE(A62,"-",H62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Limpiar filtros</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Hay filtros aplicados</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>El usuario pulsa «Limpiar filtros»</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>El sistema restablece todos los filtros y vuelve a mostrar la lista completa</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>HU0017</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Psicólogo</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>descargar el expediente completo de un estudiante</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>archivarlo y compartirlo con la familia</t>
+        </is>
+      </c>
+      <c r="G63" s="5">
+        <f>CONCATENATE("Como ",B63," quiero ",D63," para ",F63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="7">
+        <f>CONCATENATE(A63,"-",H63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Descarga exitosa</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>El estudiante tiene encuesta y predicción registradas</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>El psicólogo pulsa «Descargar Expediente»</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>El sistema genera el documento con los datos, los resultados y su explicación</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>HU0017</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="7">
+        <f>CONCATENATE(A64,"-",H64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Estudiante sin datos suficientes</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>El estudiante no tiene predicción registrada</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>El psicólogo intenta descargar el expediente</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>El sistema informa de qué información falta antes de poder generarlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>HU0018</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>que el documento de identidad se guarde cifrado</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>cumplir la Ley N.° 29733 de protección de datos personales</t>
+        </is>
+      </c>
+      <c r="G65" s="5">
+        <f>CONCATENATE("Como ",B65," quiero ",D65," para ",F65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="7">
+        <f>CONCATENATE(A65,"-",H65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Cifrado en la base de datos</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Se registra un estudiante con su documento</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Se consulta directamente la base de datos</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>El número no es legible: se almacena cifrado con Fernet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>HU0018</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="7">
+        <f>CONCATENATE(A66,"-",H66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Unicidad sin exponer el dato</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Se intenta registrar un documento ya existente</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Se envía el formulario</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>El sistema detecta el duplicado mediante una huella irreversible, sin descifrar ningún dato</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>HU0018</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="7">
+        <f>CONCATENATE(A67,"-",H67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Enmascarado en la interfaz y en la API</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Se consulta el listado de estudiantes</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Se observa la respuesta de la API</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>El número completo no viaja en el listado: solo los cuatro últimos caracteres</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>HU0019</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Usuario del sistema</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>que el sistema me pida confirmación antes de modificar datos</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>evitar cambios accidentales sobre información de menores</t>
+        </is>
+      </c>
+      <c r="G68" s="5">
+        <f>CONCATENATE("Como ",B68," quiero ",D68," para ",F68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="7">
+        <f>CONCATENATE(A68,"-",H68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>Confirmación antes de guardar</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>El usuario completa cualquier formulario que modifica datos</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Pulsa el botón de guardar</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>El sistema muestra un diálogo con el detalle de lo que va a ocurrir antes de ejecutarlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>HU0019</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="7">
+        <f>CONCATENATE(A69,"-",H69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>Cancelación sin efectos</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>El diálogo de confirmación está abierto</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>El usuario pulsa «Cancelar» o la tecla Escape</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>No se envía ninguna petición y los datos permanecen sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>HU0019</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="7">
+        <f>CONCATENATE(A70,"-",H70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
           <t>Foco en la opción segura</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>La acción es destructiva, como eliminar un estudiante</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>Se abre el diálogo de confirmación</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>El foco inicial se sitúa en «Cancelar», de modo que un Enter accidental no ejecute el borrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Usuario del sistema</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>solicitar el restablecimiento de mi contrasena cuando no puedo entrar</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>recuperar el acceso sin depender de que alguien recuerde mi clave</t>
+        </is>
+      </c>
+      <c r="G71" s="5">
+        <f>CONCATENATE("Como ",B71," quiero ",D71," para ",F71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="7">
+        <f>CONCATENATE(A71,"-",H71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Solicitud registrada</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>El usuario olvido su contrasena y esta en la pantalla de acceso</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Pulsa «Olvidaste tu contrasena», escribe su usuario y confirma</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>El sistema registra la peticion, la deja pendiente durante 72 horas e indica que debe acudir al administrador; no se envia ningun correo ni mensaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="7">
+        <f>CONCATENATE(A72,"-",H72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>La respuesta no revela si la cuenta existe</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Alguien escribe un usuario que no esta registrado</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Envia la solicitud de restablecimiento</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>El sistema responde exactamente el mismo mensaje que para una cuenta real, de modo que no se pueda averiguar que usuarios existen probando nombres</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" s="7">
+        <f>CONCATENATE(A73,"-",H73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>Una sola peticion viva por cuenta</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>El usuario ya tiene una solicitud pendiente sin atender</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Vuelve a solicitar el restablecimiento</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>El sistema renueva la vigencia de la peticion existente en lugar de crear otra, para que la bandeja del administrador no acumule duplicados</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" s="7">
+        <f>CONCATENATE(A74,"-",H74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>La solicitud caduca sola</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Han pasado mas de 72 horas desde la peticion</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>El administrador abre la bandeja de solicitudes</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>La peticion aparece como «caducada» y ya no se puede atender, sin que nadie haya tenido que ejecutar ninguna tarea de limpieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>restablecer la contrasena de una cuenta que lo ha solicitado</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>devolver el acceso a un companero sin conocer su contrasena anterior</t>
+        </is>
+      </c>
+      <c r="G75" s="5">
+        <f>CONCATENATE("Como ",B75," quiero ",D75," para ",F75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="7">
+        <f>CONCATENATE(A75,"-",H75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>Solo el administrador accede a la bandeja</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Un docente o un psicologo inicia sesion</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Intenta abrir «Accesos y Seguridad» o llamar directamente a la API</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>El sistema deniega el acceso con codigo 403; la comprobacion se hace en el servidor y no depende de que la opcion este oculta en el menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="7">
+        <f>CONCATENATE(A76,"-",H76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>Restablecimiento aplicado</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Existe una solicitud pendiente de un usuario</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>El administrador escribe la contrasena nueva y confirma en el dialogo</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>El sistema guarda la contrasena cifrada, marca la solicitud como atendida e indica que debe comunicarse en persona porque no se envia por ningun medio</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="7">
+        <f>CONCATENATE(A77,"-",H77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>Las sesiones abiertas se cierran</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>El usuario afectado tenia sesiones activas en otros equipos</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>El administrador completa el restablecimiento</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>El sistema revoca todas sus sesiones, porque si pidio recuperar el acceso cabe la posibilidad de que otra persona lo tuviera</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" s="7">
+        <f>CONCATENATE(A78,"-",H78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>Una solicitud atendida no se reutiliza</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>La solicitud ya fue atendida o caduco</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Se intenta atenderla de nuevo</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>El sistema responde con codigo 409 e indica en que estado se encuentra, en lugar de cambiar la contrasena por segunda vez</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I79" s="7">
+        <f>CONCATENATE(A79,"-",H79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>La contrasena nueva debe ser valida</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>El administrador esta atendiendo una solicitud</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Escribe una contrasena que no cumple la longitud minima</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>El sistema la rechaza explicando el motivo y la solicitud sigue pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>ver el estado de las cuentas y las sesiones abiertas</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>poder cerrar un acceso que quedo abierto en un aula</t>
+        </is>
+      </c>
+      <c r="G80" s="5">
+        <f>CONCATENATE("Como ",B80," quiero ",D80," para ",F80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="7">
+        <f>CONCATENATE(A80,"-",H80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>Inventario de cuentas</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>El administrador entra en «Accesos y Seguridad»</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Consulta la seccion de cuentas del sistema</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>El sistema lista cada cuenta con su rol, su ultimo acceso y cuantas sesiones tiene abiertas en ese momento</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" s="7">
+        <f>CONCATENATE(A81,"-",H81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>Cierre de sesiones sin cambiar la contrasena</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Una cuenta tiene sesiones abiertas</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>El administrador pulsa «Cerrar sesiones» y confirma</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>El sistema revoca esas sesiones y la contrasena permanece intacta, de modo que la persona puede volver a entrar con la que ya conoce</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" s="7">
+        <f>CONCATENATE(A82,"-",H82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>Aviso al cerrar la propia sesion</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>El administrador va a cerrar las sesiones de su propia cuenta</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Se abre el dialogo de confirmacion</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>El sistema advierte de que se cerrara tambien la suya y tendra que volver a entrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I83" s="7">
+        <f>CONCATENATE(A83,"-",H83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>Matriz de permisos derivada de la configuracion</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>El administrador consulta que ve cada rol</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Revisa la tabla de permisos</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>La tabla se genera a partir de la configuracion real de permisos y no de un texto escrito a mano, de modo que no puede quedar desfasada respecto al sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Docente o Psicologo</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Necesito:</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>conocer cuanto acierta el modelo y en que se fija</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Con la finalidad de:</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>interpretar una prediccion sabiendo su margen de error y no como un veredicto</t>
+        </is>
+      </c>
+      <c r="G84" s="5">
+        <f>CONCATENATE("Como ",B84," quiero ",D84," para ",F84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="7">
+        <f>CONCATENATE(A84,"-",H84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>Fiabilidad medida con estudiantes reales</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>El usuario abre «Metricas del Modelo»</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Consulta el encabezado de cada modelo</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>El sistema muestra el porcentaje de acierto sobre los 30 estudiantes reales, con su matriz de confusion y el desglose por nivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" s="7">
+        <f>CONCATENATE(A85,"-",H85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>Se distinguen los dos conjuntos de datos</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Conviven la validacion de entrenamiento y la validacion real</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>El usuario recorre la pantalla</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>El sistema separa y explica ambas: 500 registros sinteticos repartidos en 400 de entrenamiento y 100 de validacion, frente a 30 estudiantes reales con dictamen profesional, indicando para que sirve cada una</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" s="7">
+        <f>CONCATENATE(A86,"-",H86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>Influencia de cada variable</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>El usuario quiere saber en que se fija el modelo</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Consulta la seccion de influencia</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>El sistema muestra el peso de cada variable del modelo de riesgo y de cada subescala del EDAH, aclarando que explica el modelo en conjunto y no un caso concreto</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I87" s="7">
+        <f>CONCATENATE(A87,"-",H87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>Advertencia de tamizaje</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>El usuario consulta cualquier cifra de la pantalla</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Lee el encabezado y el cierre de la vista</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>El sistema advierte de que es una herramienta de tamizaje y no de diagnostico, y explica que consecuencia tiene cada tipo de error</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I88" s="7">
+        <f>CONCATENATE(A88,"-",H88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>Aviso en los niveles con pocos casos</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Un nivel de la validacion real tiene menos de cinco estudiantes</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>El usuario consulta el desglose por nivel</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>El sistema advierte de que ese porcentaje es poco fiable, porque un solo acierto o fallo lo mueve decenas de puntos</t>
         </is>
       </c>
     </row>
